--- a/daily_nse_scans/final-watch-list.xlsx
+++ b/daily_nse_scans/final-watch-list.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Equities-ShareMarket\simple_stock_scanner\daily_nse_scans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E52D22-99B0-4E65-889E-712D4543BDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02572653-701E-489D-8519-D933644C9655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="only_uptrend" sheetId="2" r:id="rId2"/>
+    <sheet name="slowly-moving-up" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="149">
   <si>
     <t>symbol</t>
   </si>
@@ -97,13 +99,388 @@
   </si>
   <si>
     <t>this is lookging good</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>CENTUM</t>
+  </si>
+  <si>
+    <t>uptrend</t>
+  </si>
+  <si>
+    <t>SIGMAADV</t>
+  </si>
+  <si>
+    <t>CYIENTDLM</t>
+  </si>
+  <si>
+    <t>waiting for comeback</t>
+  </si>
+  <si>
+    <t>slow moving but uptrend</t>
+  </si>
+  <si>
+    <t>WHEELS</t>
+  </si>
+  <si>
+    <t>MENONBE</t>
+  </si>
+  <si>
+    <t>KROSS</t>
+  </si>
+  <si>
+    <t>better to avoid</t>
+  </si>
+  <si>
+    <t>SSWL</t>
+  </si>
+  <si>
+    <t>wait for positive symbol in this</t>
+  </si>
+  <si>
+    <t>VARROC</t>
+  </si>
+  <si>
+    <t>sideways</t>
+  </si>
+  <si>
+    <t>INDNIPPON</t>
+  </si>
+  <si>
+    <t>check tomorw if it goes up or not, if it goes then u can buy else ignore</t>
+  </si>
+  <si>
+    <t>SUNDRMFAST</t>
+  </si>
+  <si>
+    <t>RML</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>put small amount into this stock as its in long term uptrend</t>
+  </si>
+  <si>
+    <t>TALBROAUTO</t>
+  </si>
+  <si>
+    <t>SMLMAH</t>
+  </si>
+  <si>
+    <t>this is at its all time high, can go up, wait and watch</t>
+  </si>
+  <si>
+    <t>WSTCSTPAPR</t>
+  </si>
+  <si>
+    <t>VALIANTORG</t>
+  </si>
+  <si>
+    <t>can buy aftr checking uptrend</t>
+  </si>
+  <si>
+    <t>be watchfull as its touching the highest ever resistance</t>
+  </si>
+  <si>
+    <t>OAL</t>
+  </si>
+  <si>
+    <t>VISHNU</t>
+  </si>
+  <si>
+    <t>highest ever price</t>
+  </si>
+  <si>
+    <t>BODALCHEM</t>
+  </si>
+  <si>
+    <t>watchout as it gave good returns</t>
+  </si>
+  <si>
+    <t>watchout slowly moving up</t>
+  </si>
+  <si>
+    <t>BHAGERIA</t>
+  </si>
+  <si>
+    <t>watchout, it went really well, need to look into it</t>
+  </si>
+  <si>
+    <t>RGL</t>
+  </si>
+  <si>
+    <t>SKYGOLD</t>
+  </si>
+  <si>
+    <t>STOVEKRAFT</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>BIL</t>
+  </si>
+  <si>
+    <t>watchout as its at top its all time high</t>
+  </si>
+  <si>
+    <t>PGIL</t>
+  </si>
+  <si>
+    <t>EMIL</t>
+  </si>
+  <si>
+    <t>ANTELOPUS</t>
+  </si>
+  <si>
+    <t>watchout, cant say where its going</t>
+  </si>
+  <si>
+    <t>DOLPHIN</t>
+  </si>
+  <si>
+    <t>can increase, its in uptrend</t>
+  </si>
+  <si>
+    <t>PRABHA</t>
+  </si>
+  <si>
+    <t>its in uptrend, may go up after brief break</t>
+  </si>
+  <si>
+    <t>HINDOILEXP</t>
+  </si>
+  <si>
+    <t>slowly moving up</t>
+  </si>
+  <si>
+    <t>DEEPINDS</t>
+  </si>
+  <si>
+    <t>it went up but now slowed</t>
+  </si>
+  <si>
+    <t>ASIANENE</t>
+  </si>
+  <si>
+    <t>its in uptrend but may go ahead</t>
+  </si>
+  <si>
+    <t>TNPETRO</t>
+  </si>
+  <si>
+    <t>CHENNPETRO</t>
+  </si>
+  <si>
+    <t>slowly going up</t>
+  </si>
+  <si>
+    <t>SHAREINDIA</t>
+  </si>
+  <si>
+    <t>VENUSPIPES</t>
+  </si>
+  <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>QUADFUTURE</t>
+  </si>
+  <si>
+    <t>MOREPENLAB</t>
+  </si>
+  <si>
+    <t>BIRLACABLE</t>
+  </si>
+  <si>
+    <t>OMAXE</t>
+  </si>
+  <si>
+    <t>WELSPUNLIV</t>
+  </si>
+  <si>
+    <t>NOVARTIND</t>
+  </si>
+  <si>
+    <t>KIRIINDUS</t>
+  </si>
+  <si>
+    <t>SOLARA</t>
+  </si>
+  <si>
+    <t>MANINDS</t>
+  </si>
+  <si>
+    <t>WINDLAS</t>
+  </si>
+  <si>
+    <t>REDINGTON</t>
+  </si>
+  <si>
+    <t>RISHABH</t>
+  </si>
+  <si>
+    <t>FINCABLES</t>
+  </si>
+  <si>
+    <t>LAURUSLABS</t>
+  </si>
+  <si>
+    <t>SAKAR</t>
+  </si>
+  <si>
+    <t>GMMPFAUDLR</t>
+  </si>
+  <si>
+    <t>ANTHEM</t>
+  </si>
+  <si>
+    <t>BEPL</t>
+  </si>
+  <si>
+    <t>DIVISLAB</t>
+  </si>
+  <si>
+    <t>VINDHYATEL</t>
+  </si>
+  <si>
+    <t>MACPOWER</t>
+  </si>
+  <si>
+    <t>LALPATHLAB</t>
+  </si>
+  <si>
+    <t>IOLCP</t>
+  </si>
+  <si>
+    <t>BLISSGVS</t>
+  </si>
+  <si>
+    <t>WELCORP</t>
+  </si>
+  <si>
+    <t>INNOVACAP</t>
+  </si>
+  <si>
+    <t>RSWM</t>
+  </si>
+  <si>
+    <t>WELENT</t>
+  </si>
+  <si>
+    <t>JYOTICNC</t>
+  </si>
+  <si>
+    <t>GUFICBIO</t>
+  </si>
+  <si>
+    <t>ALIVUS</t>
+  </si>
+  <si>
+    <t>MANORAMA</t>
+  </si>
+  <si>
+    <t>STLTECH</t>
+  </si>
+  <si>
+    <t>IPCALAB</t>
+  </si>
+  <si>
+    <t>WABAG</t>
+  </si>
+  <si>
+    <t>E2E</t>
+  </si>
+  <si>
+    <t>PTCIL</t>
+  </si>
+  <si>
+    <t>KABRAEXTRU</t>
+  </si>
+  <si>
+    <t>SAILIFE</t>
+  </si>
+  <si>
+    <t>BOSCHLTD</t>
+  </si>
+  <si>
+    <t>TASTYBITE</t>
+  </si>
+  <si>
+    <t>ANANDRATHI</t>
+  </si>
+  <si>
+    <t>VSSL</t>
+  </si>
+  <si>
+    <t>KAPSTON</t>
+  </si>
+  <si>
+    <t>CUPID</t>
+  </si>
+  <si>
+    <t>ARROWGREEN</t>
+  </si>
+  <si>
+    <t>COMSYN</t>
+  </si>
+  <si>
+    <t>AKUMS</t>
+  </si>
+  <si>
+    <t>HERITGFOOD</t>
+  </si>
+  <si>
+    <t>RUBYMILLS</t>
+  </si>
+  <si>
+    <t>SPECTRUM</t>
+  </si>
+  <si>
+    <t>MODISONLTD</t>
+  </si>
+  <si>
+    <t>EIMCOELECO</t>
+  </si>
+  <si>
+    <t>PAYTM</t>
+  </si>
+  <si>
+    <t>RAYMOND</t>
+  </si>
+  <si>
+    <t>ACMESOLAR</t>
+  </si>
+  <si>
+    <t>SHANTIGEAR</t>
+  </si>
+  <si>
+    <t>HATSUN</t>
+  </si>
+  <si>
+    <t>DIACABS</t>
+  </si>
+  <si>
+    <t>SETL</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>watch n buy</t>
+  </si>
+  <si>
+    <t>Symbol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +490,20 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF17202A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -140,9 +531,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,10 +824,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.21875" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="75.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -434,6 +835,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -538,6 +942,1018 @@
       </c>
       <c r="B19" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D401CA4-15AD-479A-A787-4A2E6F8B51F8}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6659F068-C7D0-4076-BA43-58B99F2E1D9C}">
+  <dimension ref="A2:A54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
